--- a/Methanol/Methanol_Brownfield_Memmingen_Bio_H2/Datenbank.xlsx
+++ b/Methanol/Methanol_Brownfield_Memmingen_Bio_H2/Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Brownfield_Memmingen_Bio_H2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B784CBFB-5302-4899-97E4-D9B7925D5C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A5E895-BB5A-4DEC-BE9C-3218ACCCB890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="395">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1352,6 +1352,21 @@
   </si>
   <si>
     <t>calc_h2bezug_kosten</t>
+  </si>
+  <si>
+    <t>Verkaufspreiseanalyse</t>
+  </si>
+  <si>
+    <t>Maximaler Verkaufspreis Bilanznull</t>
+  </si>
+  <si>
+    <t>calc_maxprice</t>
+  </si>
+  <si>
+    <t>Verkaufspreis Bilanznull mit Vorverkauf</t>
+  </si>
+  <si>
+    <t>calc_price</t>
   </si>
 </sst>
 </file>
@@ -1576,6 +1591,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1624,11 +1644,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2000,10 +2015,10 @@
       <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="59" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2020,8 +2035,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="54"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="57"/>
       <c r="C3" s="1" t="s">
         <v>84</v>
       </c>
@@ -2036,8 +2051,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="46"/>
-      <c r="B4" s="54"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="57"/>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
@@ -2052,8 +2067,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="54"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="57"/>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2068,8 +2083,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="46"/>
-      <c r="B6" s="54"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="57"/>
       <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2084,8 +2099,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="46"/>
-      <c r="B7" s="54"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="57"/>
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
@@ -2100,8 +2115,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="46"/>
-      <c r="B8" s="57" t="s">
+      <c r="A8" s="49"/>
+      <c r="B8" s="60" t="s">
         <v>231</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -2118,8 +2133,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="46"/>
-      <c r="B9" s="54"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="57"/>
       <c r="C9" s="1" t="s">
         <v>85</v>
       </c>
@@ -2134,8 +2149,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="54"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
@@ -2150,8 +2165,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
-      <c r="B11" s="54"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="57"/>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
@@ -2166,8 +2181,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="46"/>
-      <c r="B12" s="54"/>
+      <c r="A12" s="49"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="1" t="s">
         <v>86</v>
       </c>
@@ -2182,8 +2197,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
-      <c r="B13" s="54"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="57"/>
       <c r="C13" s="1" t="s">
         <v>246</v>
       </c>
@@ -2198,8 +2213,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
-      <c r="B14" s="54"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
@@ -2214,8 +2229,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
-      <c r="B15" s="58"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="13" t="s">
         <v>15</v>
       </c>
@@ -2230,8 +2245,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
-      <c r="B16" s="57" t="s">
+      <c r="A16" s="49"/>
+      <c r="B16" s="60" t="s">
         <v>273</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -2248,8 +2263,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="46"/>
-      <c r="B17" s="54"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="57"/>
       <c r="C17" s="1" t="s">
         <v>84</v>
       </c>
@@ -2264,8 +2279,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
-      <c r="B18" s="54"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="57"/>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
@@ -2280,8 +2295,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
-      <c r="B19" s="54"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="57"/>
       <c r="C19" s="1" t="s">
         <v>11</v>
       </c>
@@ -2296,8 +2311,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="46"/>
-      <c r="B20" s="54"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="57"/>
       <c r="C20" s="1" t="s">
         <v>13</v>
       </c>
@@ -2312,8 +2327,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="46"/>
-      <c r="B21" s="58"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="13" t="s">
         <v>15</v>
       </c>
@@ -2328,8 +2343,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="46"/>
-      <c r="B22" s="59" t="s">
+      <c r="A22" s="49"/>
+      <c r="B22" s="62" t="s">
         <v>342</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2346,8 +2361,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="46"/>
-      <c r="B23" s="59"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="62"/>
       <c r="C23" s="1" t="s">
         <v>283</v>
       </c>
@@ -2362,8 +2377,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="46"/>
-      <c r="B24" s="59"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="62"/>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
@@ -2378,8 +2393,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="46"/>
-      <c r="B25" s="59"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="62"/>
       <c r="C25" s="1" t="s">
         <v>379</v>
       </c>
@@ -2394,8 +2409,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="46"/>
-      <c r="B26" s="59"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="62"/>
       <c r="C26" s="1" t="s">
         <v>372</v>
       </c>
@@ -2410,8 +2425,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="46"/>
-      <c r="B27" s="59"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="62"/>
       <c r="C27" s="1" t="s">
         <v>355</v>
       </c>
@@ -2426,8 +2441,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="46"/>
-      <c r="B28" s="59"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="62"/>
       <c r="C28" s="1" t="s">
         <v>380</v>
       </c>
@@ -2442,8 +2457,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="46"/>
-      <c r="B29" s="59"/>
+      <c r="A29" s="49"/>
+      <c r="B29" s="62"/>
       <c r="C29" s="1" t="s">
         <v>13</v>
       </c>
@@ -2458,8 +2473,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="46"/>
-      <c r="B30" s="59"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="62"/>
       <c r="C30" s="1" t="s">
         <v>15</v>
       </c>
@@ -2474,10 +2489,10 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="52" t="s">
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2494,8 +2509,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="46"/>
-      <c r="B32" s="50"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="53"/>
       <c r="C32" s="1" t="s">
         <v>11</v>
       </c>
@@ -2510,8 +2525,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="46"/>
-      <c r="B33" s="50"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="53"/>
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
@@ -2526,8 +2541,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="46"/>
-      <c r="B34" s="50"/>
+      <c r="A34" s="49"/>
+      <c r="B34" s="53"/>
       <c r="C34" s="1" t="s">
         <v>20</v>
       </c>
@@ -2542,8 +2557,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="46"/>
-      <c r="B35" s="50"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="53"/>
       <c r="C35" s="1" t="s">
         <v>35</v>
       </c>
@@ -2558,8 +2573,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="46"/>
-      <c r="B36" s="50"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="53"/>
       <c r="C36" s="1" t="s">
         <v>36</v>
       </c>
@@ -2574,8 +2589,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="50"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="53"/>
       <c r="C37" s="1" t="s">
         <v>15</v>
       </c>
@@ -2590,8 +2605,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="46"/>
-      <c r="B38" s="51"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="54"/>
       <c r="C38" s="13" t="s">
         <v>88</v>
       </c>
@@ -2606,8 +2621,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
-      <c r="B39" s="52" t="s">
+      <c r="A39" s="49"/>
+      <c r="B39" s="55" t="s">
         <v>317</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2624,8 +2639,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
-      <c r="B40" s="50"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="53"/>
       <c r="C40" s="1" t="s">
         <v>11</v>
       </c>
@@ -2640,8 +2655,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
-      <c r="B41" s="50"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="53"/>
       <c r="C41" s="1" t="s">
         <v>13</v>
       </c>
@@ -2656,8 +2671,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
-      <c r="B42" s="50"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="53"/>
       <c r="C42" s="1" t="s">
         <v>20</v>
       </c>
@@ -2672,8 +2687,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="50"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="53"/>
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
@@ -2688,8 +2703,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
-      <c r="B44" s="50"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="53"/>
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -2704,8 +2719,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="46"/>
-      <c r="B45" s="50"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="53"/>
       <c r="C45" s="1" t="s">
         <v>15</v>
       </c>
@@ -2720,8 +2735,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="46"/>
-      <c r="B46" s="50"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="53"/>
       <c r="C46" s="13" t="s">
         <v>88</v>
       </c>
@@ -2736,8 +2751,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="46"/>
-      <c r="B47" s="52" t="s">
+      <c r="A47" s="49"/>
+      <c r="B47" s="55" t="s">
         <v>203</v>
       </c>
       <c r="C47" s="11" t="s">
@@ -2754,8 +2769,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="46"/>
-      <c r="B48" s="54"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="57"/>
       <c r="C48" s="1" t="s">
         <v>21</v>
       </c>
@@ -2771,8 +2786,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="54"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="57"/>
       <c r="C49" s="1" t="s">
         <v>16</v>
       </c>
@@ -2787,8 +2802,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="46"/>
-      <c r="B50" s="54"/>
+      <c r="A50" s="49"/>
+      <c r="B50" s="57"/>
       <c r="C50" s="1" t="s">
         <v>17</v>
       </c>
@@ -2803,8 +2818,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="46"/>
-      <c r="B51" s="54"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="57"/>
       <c r="C51" s="1" t="s">
         <v>35</v>
       </c>
@@ -2819,8 +2834,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="46"/>
-      <c r="B52" s="54"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="57"/>
       <c r="C52" s="1" t="s">
         <v>36</v>
       </c>
@@ -2835,8 +2850,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
-      <c r="B53" s="54"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="57"/>
       <c r="C53" s="1" t="s">
         <v>89</v>
       </c>
@@ -2851,8 +2866,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
-      <c r="B54" s="54"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="57"/>
       <c r="C54" s="1" t="s">
         <v>88</v>
       </c>
@@ -2867,8 +2882,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
-      <c r="B55" s="54"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="57"/>
       <c r="C55" s="1" t="s">
         <v>13</v>
       </c>
@@ -2883,8 +2898,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="47"/>
-      <c r="B56" s="55"/>
+      <c r="A56" s="50"/>
+      <c r="B56" s="58"/>
       <c r="C56" s="17" t="s">
         <v>15</v>
       </c>
@@ -2899,7 +2914,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="48" t="s">
         <v>72</v>
       </c>
       <c r="B57" s="30" t="s">
@@ -2919,25 +2934,25 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48"/>
-      <c r="B58" s="61" t="s">
+      <c r="A58" s="51"/>
+      <c r="B58" s="45" t="s">
         <v>382</v>
       </c>
-      <c r="C58" s="62" t="s">
+      <c r="C58" s="46" t="s">
         <v>383</v>
       </c>
-      <c r="D58" s="62" t="s">
+      <c r="D58" s="46" t="s">
         <v>384</v>
       </c>
-      <c r="E58" s="63">
+      <c r="E58" s="47">
         <v>5</v>
       </c>
-      <c r="F58" s="62" t="s">
+      <c r="F58" s="46" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="48"/>
+      <c r="A59" s="51"/>
       <c r="B59" s="27" t="s">
         <v>343</v>
       </c>
@@ -2955,8 +2970,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="46"/>
-      <c r="B60" s="52" t="s">
+      <c r="A60" s="49"/>
+      <c r="B60" s="55" t="s">
         <v>4</v>
       </c>
       <c r="C60" s="11" t="s">
@@ -2973,8 +2988,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="46"/>
-      <c r="B61" s="50"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="53"/>
       <c r="C61" s="1" t="s">
         <v>10</v>
       </c>
@@ -2989,8 +3004,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="46"/>
-      <c r="B62" s="50"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="53"/>
       <c r="C62" s="1" t="s">
         <v>17</v>
       </c>
@@ -3005,8 +3020,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="46"/>
-      <c r="B63" s="50"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="53"/>
       <c r="C63" s="1" t="s">
         <v>18</v>
       </c>
@@ -3021,8 +3036,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="46"/>
-      <c r="B64" s="50"/>
+      <c r="A64" s="49"/>
+      <c r="B64" s="53"/>
       <c r="C64" s="1" t="s">
         <v>13</v>
       </c>
@@ -3037,8 +3052,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="46"/>
-      <c r="B65" s="50"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="53"/>
       <c r="C65" s="1" t="s">
         <v>68</v>
       </c>
@@ -3053,8 +3068,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="46"/>
-      <c r="B66" s="51"/>
+      <c r="A66" s="49"/>
+      <c r="B66" s="54"/>
       <c r="C66" s="13" t="s">
         <v>15</v>
       </c>
@@ -3069,8 +3084,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="46"/>
-      <c r="B67" s="52" t="s">
+      <c r="A67" s="49"/>
+      <c r="B67" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C67" s="11" t="s">
@@ -3087,8 +3102,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
-      <c r="B68" s="50"/>
+      <c r="A68" s="49"/>
+      <c r="B68" s="53"/>
       <c r="C68" s="1" t="s">
         <v>10</v>
       </c>
@@ -3103,8 +3118,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="46"/>
-      <c r="B69" s="50"/>
+      <c r="A69" s="49"/>
+      <c r="B69" s="53"/>
       <c r="C69" s="1" t="s">
         <v>17</v>
       </c>
@@ -3119,8 +3134,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="46"/>
-      <c r="B70" s="50"/>
+      <c r="A70" s="49"/>
+      <c r="B70" s="53"/>
       <c r="C70" s="1" t="s">
         <v>18</v>
       </c>
@@ -3135,8 +3150,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="46"/>
-      <c r="B71" s="50"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="53"/>
       <c r="C71" s="1" t="s">
         <v>13</v>
       </c>
@@ -3151,8 +3166,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="46"/>
-      <c r="B72" s="50"/>
+      <c r="A72" s="49"/>
+      <c r="B72" s="53"/>
       <c r="C72" s="1" t="s">
         <v>68</v>
       </c>
@@ -3167,8 +3182,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="47"/>
-      <c r="B73" s="53"/>
+      <c r="A73" s="50"/>
+      <c r="B73" s="56"/>
       <c r="C73" s="17" t="s">
         <v>15</v>
       </c>
@@ -3183,7 +3198,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="45" t="s">
+      <c r="A74" s="48" t="s">
         <v>76</v>
       </c>
       <c r="B74" s="33" t="s">
@@ -3203,7 +3218,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="46"/>
+      <c r="A75" s="49"/>
       <c r="B75" s="22" t="s">
         <v>299</v>
       </c>
@@ -3221,7 +3236,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="46"/>
+      <c r="A76" s="49"/>
       <c r="B76" s="24" t="s">
         <v>79</v>
       </c>
@@ -3239,7 +3254,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="47"/>
+      <c r="A77" s="50"/>
       <c r="B77" s="4" t="s">
         <v>262</v>
       </c>
@@ -3280,7 +3295,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
@@ -3313,10 +3328,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="59" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3331,8 +3346,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="54"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="57"/>
       <c r="C3" s="1" t="s">
         <v>108</v>
       </c>
@@ -3345,8 +3360,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="46"/>
-      <c r="B4" s="54"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="57"/>
       <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
@@ -3359,8 +3374,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="54"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="57"/>
       <c r="C5" s="1" t="s">
         <v>139</v>
       </c>
@@ -3373,8 +3388,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="46"/>
-      <c r="B6" s="54"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="57"/>
       <c r="C6" s="1" t="s">
         <v>142</v>
       </c>
@@ -3387,8 +3402,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="46"/>
-      <c r="B7" s="54"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="57"/>
       <c r="C7" s="1" t="s">
         <v>156</v>
       </c>
@@ -3401,8 +3416,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="46"/>
-      <c r="B8" s="54"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="57"/>
       <c r="C8" s="1" t="s">
         <v>198</v>
       </c>
@@ -3415,8 +3430,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="46"/>
-      <c r="B9" s="54"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="57"/>
       <c r="C9" s="1" t="s">
         <v>168</v>
       </c>
@@ -3429,8 +3444,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="54"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="1" t="s">
         <v>190</v>
       </c>
@@ -3443,13 +3458,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
-      <c r="B11" s="54"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="57"/>
       <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="46"/>
-      <c r="B12" s="57" t="s">
+      <c r="A12" s="49"/>
+      <c r="B12" s="60" t="s">
         <v>231</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -3464,8 +3479,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
-      <c r="B13" s="54"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="57"/>
       <c r="C13" s="1" t="s">
         <v>255</v>
       </c>
@@ -3478,8 +3493,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
-      <c r="B14" s="54"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="1" t="s">
         <v>140</v>
       </c>
@@ -3492,8 +3507,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
-      <c r="B15" s="54"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="57"/>
       <c r="C15" s="1" t="s">
         <v>256</v>
       </c>
@@ -3506,8 +3521,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
-      <c r="B16" s="54"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="57"/>
       <c r="C16" s="1" t="s">
         <v>84</v>
       </c>
@@ -3520,8 +3535,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="46"/>
-      <c r="B17" s="54"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="57"/>
       <c r="C17" s="1" t="s">
         <v>142</v>
       </c>
@@ -3534,8 +3549,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
-      <c r="B18" s="54"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="57"/>
       <c r="C18" s="1" t="s">
         <v>156</v>
       </c>
@@ -3548,8 +3563,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
-      <c r="B19" s="54"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="57"/>
       <c r="C19" s="1" t="s">
         <v>198</v>
       </c>
@@ -3562,8 +3577,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="46"/>
-      <c r="B20" s="54"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="57"/>
       <c r="C20" s="1" t="s">
         <v>168</v>
       </c>
@@ -3576,8 +3591,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="46"/>
-      <c r="B21" s="54"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="57"/>
       <c r="C21" s="1" t="s">
         <v>190</v>
       </c>
@@ -3590,16 +3605,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="46"/>
-      <c r="B22" s="58"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="14"/>
       <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="46"/>
-      <c r="B23" s="57" t="s">
+      <c r="A23" s="49"/>
+      <c r="B23" s="60" t="s">
         <v>273</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -3614,8 +3629,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="46"/>
-      <c r="B24" s="54"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="57"/>
       <c r="C24" s="1" t="s">
         <v>108</v>
       </c>
@@ -3628,8 +3643,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="46"/>
-      <c r="B25" s="54"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="57"/>
       <c r="C25" s="1" t="s">
         <v>84</v>
       </c>
@@ -3642,8 +3657,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="46"/>
-      <c r="B26" s="54"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="57"/>
       <c r="C26" s="1" t="s">
         <v>295</v>
       </c>
@@ -3656,8 +3671,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="46"/>
-      <c r="B27" s="54"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="57"/>
       <c r="C27" s="1" t="s">
         <v>142</v>
       </c>
@@ -3670,8 +3685,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="46"/>
-      <c r="B28" s="54"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="57"/>
       <c r="C28" s="1" t="s">
         <v>156</v>
       </c>
@@ -3684,8 +3699,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="46"/>
-      <c r="B29" s="54"/>
+      <c r="A29" s="49"/>
+      <c r="B29" s="57"/>
       <c r="C29" s="1" t="s">
         <v>198</v>
       </c>
@@ -3698,8 +3713,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="46"/>
-      <c r="B30" s="54"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="57"/>
       <c r="C30" s="1" t="s">
         <v>168</v>
       </c>
@@ -3712,8 +3727,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="46"/>
-      <c r="B31" s="54"/>
+      <c r="A31" s="49"/>
+      <c r="B31" s="57"/>
       <c r="C31" s="1" t="s">
         <v>190</v>
       </c>
@@ -3726,16 +3741,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="46"/>
-      <c r="B32" s="58"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="61"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
       <c r="E32" s="14"/>
       <c r="F32" s="13"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="46"/>
-      <c r="B33" s="59" t="s">
+      <c r="A33" s="49"/>
+      <c r="B33" s="62" t="s">
         <v>360</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -3750,8 +3765,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="46"/>
-      <c r="B34" s="59"/>
+      <c r="A34" s="49"/>
+      <c r="B34" s="62"/>
       <c r="C34" s="1" t="s">
         <v>108</v>
       </c>
@@ -3764,8 +3779,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="46"/>
-      <c r="B35" s="59"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="62"/>
       <c r="C35" s="1" t="s">
         <v>84</v>
       </c>
@@ -3778,8 +3793,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="46"/>
-      <c r="B36" s="59"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="62"/>
       <c r="C36" s="1" t="s">
         <v>283</v>
       </c>
@@ -3792,8 +3807,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="59"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="62"/>
       <c r="C37" s="1" t="s">
         <v>372</v>
       </c>
@@ -3806,8 +3821,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="46"/>
-      <c r="B38" s="59"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="62"/>
       <c r="C38" s="1" t="s">
         <v>260</v>
       </c>
@@ -3820,8 +3835,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
-      <c r="B39" s="59"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="62"/>
       <c r="C39" s="1" t="s">
         <v>142</v>
       </c>
@@ -3834,8 +3849,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
-      <c r="B40" s="59"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="62"/>
       <c r="C40" s="1" t="s">
         <v>156</v>
       </c>
@@ -3848,8 +3863,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
-      <c r="B41" s="59"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="62"/>
       <c r="C41" s="1" t="s">
         <v>162</v>
       </c>
@@ -3862,8 +3877,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
-      <c r="B42" s="59"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="62"/>
       <c r="C42" s="1" t="s">
         <v>198</v>
       </c>
@@ -3876,8 +3891,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="59"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="62"/>
       <c r="C43" s="1" t="s">
         <v>168</v>
       </c>
@@ -3890,8 +3905,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
-      <c r="B44" s="59"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="62"/>
       <c r="C44" s="1" t="s">
         <v>190</v>
       </c>
@@ -3904,15 +3919,15 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="46"/>
-      <c r="B45" s="59"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="62"/>
       <c r="E45" s="9"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="49" t="s">
+      <c r="B46" s="52" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -3927,8 +3942,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="46"/>
-      <c r="B47" s="50"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="53"/>
       <c r="C47" s="1" t="s">
         <v>112</v>
       </c>
@@ -3941,8 +3956,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="46"/>
-      <c r="B48" s="50"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="53"/>
       <c r="C48" s="1" t="s">
         <v>136</v>
       </c>
@@ -3955,8 +3970,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="50"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="53"/>
       <c r="C49" s="1" t="s">
         <v>137</v>
       </c>
@@ -3969,8 +3984,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="46"/>
-      <c r="B50" s="50"/>
+      <c r="A50" s="49"/>
+      <c r="B50" s="53"/>
       <c r="C50" s="1" t="s">
         <v>142</v>
       </c>
@@ -3983,8 +3998,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="46"/>
-      <c r="B51" s="50"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="53"/>
       <c r="C51" s="1" t="s">
         <v>156</v>
       </c>
@@ -3997,8 +4012,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="46"/>
-      <c r="B52" s="50"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="53"/>
       <c r="C52" s="1" t="s">
         <v>198</v>
       </c>
@@ -4011,8 +4026,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
-      <c r="B53" s="50"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="53"/>
       <c r="C53" s="1" t="s">
         <v>168</v>
       </c>
@@ -4025,8 +4040,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
-      <c r="B54" s="50"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="53"/>
       <c r="C54" s="1" t="s">
         <v>190</v>
       </c>
@@ -4039,16 +4054,16 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
-      <c r="B55" s="51"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="54"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
       <c r="F55" s="13"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
-      <c r="B56" s="50" t="s">
+      <c r="A56" s="49"/>
+      <c r="B56" s="53" t="s">
         <v>317</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -4063,8 +4078,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="46"/>
-      <c r="B57" s="50"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="53"/>
       <c r="C57" s="1" t="s">
         <v>112</v>
       </c>
@@ -4077,8 +4092,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="46"/>
-      <c r="B58" s="50"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="53"/>
       <c r="C58" s="1" t="s">
         <v>136</v>
       </c>
@@ -4091,8 +4106,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="46"/>
-      <c r="B59" s="50"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="53"/>
       <c r="C59" s="1" t="s">
         <v>137</v>
       </c>
@@ -4105,8 +4120,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="46"/>
-      <c r="B60" s="50"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="53"/>
       <c r="C60" s="1" t="s">
         <v>142</v>
       </c>
@@ -4119,8 +4134,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="46"/>
-      <c r="B61" s="50"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="53"/>
       <c r="C61" s="1" t="s">
         <v>156</v>
       </c>
@@ -4133,8 +4148,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="46"/>
-      <c r="B62" s="50"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="53"/>
       <c r="C62" s="1" t="s">
         <v>198</v>
       </c>
@@ -4147,8 +4162,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="46"/>
-      <c r="B63" s="50"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="53"/>
       <c r="C63" s="1" t="s">
         <v>168</v>
       </c>
@@ -4161,8 +4176,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="46"/>
-      <c r="B64" s="50"/>
+      <c r="A64" s="49"/>
+      <c r="B64" s="53"/>
       <c r="C64" s="1" t="s">
         <v>190</v>
       </c>
@@ -4175,13 +4190,13 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="46"/>
-      <c r="B65" s="51"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="54"/>
       <c r="E65" s="9"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="46"/>
-      <c r="B66" s="52" t="s">
+      <c r="A66" s="49"/>
+      <c r="B66" s="55" t="s">
         <v>6</v>
       </c>
       <c r="C66" s="11" t="s">
@@ -4196,8 +4211,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="46"/>
-      <c r="B67" s="50"/>
+      <c r="A67" s="49"/>
+      <c r="B67" s="53"/>
       <c r="C67" s="1" t="s">
         <v>114</v>
       </c>
@@ -4210,8 +4225,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
-      <c r="B68" s="54"/>
+      <c r="A68" s="49"/>
+      <c r="B68" s="57"/>
       <c r="C68" s="1" t="s">
         <v>112</v>
       </c>
@@ -4224,8 +4239,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="46"/>
-      <c r="B69" s="54"/>
+      <c r="A69" s="49"/>
+      <c r="B69" s="57"/>
       <c r="C69" s="1" t="s">
         <v>108</v>
       </c>
@@ -4238,8 +4253,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="46"/>
-      <c r="B70" s="54"/>
+      <c r="A70" s="49"/>
+      <c r="B70" s="57"/>
       <c r="C70" s="1" t="s">
         <v>127</v>
       </c>
@@ -4252,8 +4267,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="46"/>
-      <c r="B71" s="54"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="57"/>
       <c r="C71" s="1" t="s">
         <v>128</v>
       </c>
@@ -4266,8 +4281,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="46"/>
-      <c r="B72" s="54"/>
+      <c r="A72" s="49"/>
+      <c r="B72" s="57"/>
       <c r="C72" s="1" t="s">
         <v>142</v>
       </c>
@@ -4280,8 +4295,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="46"/>
-      <c r="B73" s="54"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="57"/>
       <c r="C73" s="1" t="s">
         <v>156</v>
       </c>
@@ -4294,8 +4309,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="46"/>
-      <c r="B74" s="54"/>
+      <c r="A74" s="49"/>
+      <c r="B74" s="57"/>
       <c r="C74" s="1" t="s">
         <v>198</v>
       </c>
@@ -4308,8 +4323,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="46"/>
-      <c r="B75" s="54"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="57"/>
       <c r="C75" s="1" t="s">
         <v>168</v>
       </c>
@@ -4322,8 +4337,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="46"/>
-      <c r="B76" s="54"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="57"/>
       <c r="C76" s="1" t="s">
         <v>190</v>
       </c>
@@ -4336,18 +4351,18 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="47"/>
-      <c r="B77" s="55"/>
+      <c r="A77" s="50"/>
+      <c r="B77" s="58"/>
       <c r="C77" s="17"/>
       <c r="D77" s="17"/>
       <c r="E77" s="18"/>
       <c r="F77" s="17"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="45" t="s">
+      <c r="A78" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="56" t="s">
+      <c r="B78" s="59" t="s">
         <v>73</v>
       </c>
       <c r="C78" s="2" t="s">
@@ -4362,8 +4377,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="46"/>
-      <c r="B79" s="60"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="63"/>
       <c r="C79" s="36" t="s">
         <v>154</v>
       </c>
@@ -4376,16 +4391,16 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="46"/>
-      <c r="B80" s="58"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="61"/>
       <c r="C80" s="13"/>
       <c r="D80" s="13"/>
       <c r="E80" s="38"/>
       <c r="F80" s="13"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="46"/>
-      <c r="B81" s="57" t="s">
+      <c r="A81" s="49"/>
+      <c r="B81" s="60" t="s">
         <v>343</v>
       </c>
       <c r="C81" s="11" t="s">
@@ -4400,8 +4415,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="46"/>
-      <c r="B82" s="60"/>
+      <c r="A82" s="49"/>
+      <c r="B82" s="63"/>
       <c r="C82" s="36" t="s">
         <v>347</v>
       </c>
@@ -4414,16 +4429,16 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="46"/>
-      <c r="B83" s="58"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="61"/>
       <c r="C83" s="13"/>
       <c r="D83" s="13"/>
       <c r="E83" s="38"/>
       <c r="F83" s="13"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="46"/>
-      <c r="B84" s="60" t="s">
+      <c r="A84" s="49"/>
+      <c r="B84" s="63" t="s">
         <v>385</v>
       </c>
       <c r="C84" s="36" t="s">
@@ -4438,8 +4453,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="46"/>
-      <c r="B85" s="60"/>
+      <c r="A85" s="49"/>
+      <c r="B85" s="63"/>
       <c r="C85" s="1" t="s">
         <v>387</v>
       </c>
@@ -4452,13 +4467,13 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="46"/>
-      <c r="B86" s="60"/>
+      <c r="A86" s="49"/>
+      <c r="B86" s="63"/>
       <c r="E86" s="7"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="46"/>
-      <c r="B87" s="52" t="s">
+      <c r="A87" s="49"/>
+      <c r="B87" s="55" t="s">
         <v>4</v>
       </c>
       <c r="C87" s="11" t="s">
@@ -4473,8 +4488,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="46"/>
-      <c r="B88" s="50"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="53"/>
       <c r="C88" s="1" t="s">
         <v>108</v>
       </c>
@@ -4487,8 +4502,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="46"/>
-      <c r="B89" s="50"/>
+      <c r="A89" s="49"/>
+      <c r="B89" s="53"/>
       <c r="C89" s="1" t="s">
         <v>123</v>
       </c>
@@ -4501,8 +4516,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="46"/>
-      <c r="B90" s="50"/>
+      <c r="A90" s="49"/>
+      <c r="B90" s="53"/>
       <c r="C90" s="1" t="s">
         <v>142</v>
       </c>
@@ -4515,8 +4530,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="46"/>
-      <c r="B91" s="50"/>
+      <c r="A91" s="49"/>
+      <c r="B91" s="53"/>
       <c r="C91" s="1" t="s">
         <v>156</v>
       </c>
@@ -4529,8 +4544,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="46"/>
-      <c r="B92" s="50"/>
+      <c r="A92" s="49"/>
+      <c r="B92" s="53"/>
       <c r="C92" s="1" t="s">
         <v>162</v>
       </c>
@@ -4543,8 +4558,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="46"/>
-      <c r="B93" s="50"/>
+      <c r="A93" s="49"/>
+      <c r="B93" s="53"/>
       <c r="C93" s="1" t="s">
         <v>198</v>
       </c>
@@ -4557,8 +4572,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="46"/>
-      <c r="B94" s="50"/>
+      <c r="A94" s="49"/>
+      <c r="B94" s="53"/>
       <c r="C94" s="1" t="s">
         <v>168</v>
       </c>
@@ -4571,8 +4586,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="46"/>
-      <c r="B95" s="50"/>
+      <c r="A95" s="49"/>
+      <c r="B95" s="53"/>
       <c r="C95" s="1" t="s">
         <v>190</v>
       </c>
@@ -4585,12 +4600,12 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="46"/>
-      <c r="B96" s="51"/>
+      <c r="A96" s="49"/>
+      <c r="B96" s="54"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="46"/>
-      <c r="B97" s="52" t="s">
+      <c r="A97" s="49"/>
+      <c r="B97" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C97" s="11" t="s">
@@ -4605,8 +4620,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="46"/>
-      <c r="B98" s="50"/>
+      <c r="A98" s="49"/>
+      <c r="B98" s="53"/>
       <c r="C98" s="1" t="s">
         <v>109</v>
       </c>
@@ -4619,8 +4634,8 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="46"/>
-      <c r="B99" s="50"/>
+      <c r="A99" s="49"/>
+      <c r="B99" s="53"/>
       <c r="C99" s="1" t="s">
         <v>121</v>
       </c>
@@ -4633,8 +4648,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="46"/>
-      <c r="B100" s="50"/>
+      <c r="A100" s="49"/>
+      <c r="B100" s="53"/>
       <c r="C100" s="1" t="s">
         <v>142</v>
       </c>
@@ -4647,8 +4662,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="46"/>
-      <c r="B101" s="50"/>
+      <c r="A101" s="49"/>
+      <c r="B101" s="53"/>
       <c r="C101" s="1" t="s">
         <v>156</v>
       </c>
@@ -4661,8 +4676,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="46"/>
-      <c r="B102" s="50"/>
+      <c r="A102" s="49"/>
+      <c r="B102" s="53"/>
       <c r="C102" s="1" t="s">
         <v>162</v>
       </c>
@@ -4675,8 +4690,8 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="46"/>
-      <c r="B103" s="50"/>
+      <c r="A103" s="49"/>
+      <c r="B103" s="53"/>
       <c r="C103" s="1" t="s">
         <v>198</v>
       </c>
@@ -4689,8 +4704,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="46"/>
-      <c r="B104" s="50"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="53"/>
       <c r="C104" s="1" t="s">
         <v>168</v>
       </c>
@@ -4703,8 +4718,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="46"/>
-      <c r="B105" s="50"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="53"/>
       <c r="C105" s="1" t="s">
         <v>190</v>
       </c>
@@ -4717,14 +4732,14 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="47"/>
-      <c r="B106" s="53"/>
+      <c r="A106" s="50"/>
+      <c r="B106" s="56"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="45" t="s">
+      <c r="A107" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="B107" s="56" t="s">
+      <c r="B107" s="59" t="s">
         <v>73</v>
       </c>
       <c r="C107" s="2" t="s">
@@ -4739,8 +4754,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="46"/>
-      <c r="B108" s="54"/>
+      <c r="A108" s="49"/>
+      <c r="B108" s="57"/>
       <c r="C108" s="1" t="s">
         <v>230</v>
       </c>
@@ -4753,8 +4768,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="46"/>
-      <c r="B109" s="54"/>
+      <c r="A109" s="49"/>
+      <c r="B109" s="57"/>
       <c r="C109" s="1" t="s">
         <v>151</v>
       </c>
@@ -4767,16 +4782,16 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="46"/>
-      <c r="B110" s="58"/>
+      <c r="A110" s="49"/>
+      <c r="B110" s="61"/>
       <c r="C110" s="13"/>
       <c r="D110" s="13"/>
       <c r="E110" s="14"/>
       <c r="F110" s="13"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="46"/>
-      <c r="B111" s="57" t="s">
+      <c r="A111" s="49"/>
+      <c r="B111" s="60" t="s">
         <v>303</v>
       </c>
       <c r="C111" s="1" t="s">
@@ -4791,8 +4806,8 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="46"/>
-      <c r="B112" s="54"/>
+      <c r="A112" s="49"/>
+      <c r="B112" s="57"/>
       <c r="C112" s="1" t="s">
         <v>308</v>
       </c>
@@ -4805,8 +4820,8 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="46"/>
-      <c r="B113" s="54"/>
+      <c r="A113" s="49"/>
+      <c r="B113" s="57"/>
       <c r="C113" s="1" t="s">
         <v>309</v>
       </c>
@@ -4819,13 +4834,13 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="46"/>
-      <c r="B114" s="58"/>
+      <c r="A114" s="49"/>
+      <c r="B114" s="61"/>
       <c r="E114" s="9"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="46"/>
-      <c r="B115" s="57" t="s">
+      <c r="A115" s="49"/>
+      <c r="B115" s="60" t="s">
         <v>79</v>
       </c>
       <c r="C115" s="11" t="s">
@@ -4840,8 +4855,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="46"/>
-      <c r="B116" s="54"/>
+      <c r="A116" s="49"/>
+      <c r="B116" s="57"/>
       <c r="C116" s="1" t="s">
         <v>152</v>
       </c>
@@ -4854,16 +4869,16 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="46"/>
-      <c r="B117" s="58"/>
+      <c r="A117" s="49"/>
+      <c r="B117" s="61"/>
       <c r="C117" s="13"/>
       <c r="D117" s="13"/>
       <c r="E117" s="14"/>
       <c r="F117" s="13"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="46"/>
-      <c r="B118" s="57" t="s">
+      <c r="A118" s="49"/>
+      <c r="B118" s="60" t="s">
         <v>262</v>
       </c>
       <c r="C118" s="1" t="s">
@@ -4878,8 +4893,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="46"/>
-      <c r="B119" s="54"/>
+      <c r="A119" s="49"/>
+      <c r="B119" s="57"/>
       <c r="C119" s="1" t="s">
         <v>263</v>
       </c>
@@ -4892,18 +4907,18 @@
       </c>
     </row>
     <row r="120" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="47"/>
-      <c r="B120" s="55"/>
+      <c r="A120" s="50"/>
+      <c r="B120" s="58"/>
       <c r="C120" s="17"/>
       <c r="D120" s="17"/>
       <c r="E120" s="18"/>
       <c r="F120" s="17"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="45" t="s">
+      <c r="A121" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B121" s="56" t="s">
+      <c r="B121" s="59" t="s">
         <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
@@ -4918,8 +4933,8 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="46"/>
-      <c r="B122" s="54"/>
+      <c r="A122" s="51"/>
+      <c r="B122" s="57"/>
       <c r="C122" s="1" t="s">
         <v>175</v>
       </c>
@@ -4931,16 +4946,16 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="46"/>
-      <c r="B123" s="58"/>
+      <c r="A123" s="51"/>
+      <c r="B123" s="61"/>
       <c r="C123" s="13"/>
       <c r="D123" s="13"/>
       <c r="E123" s="13"/>
       <c r="F123" s="13"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="46"/>
-      <c r="B124" s="57" t="s">
+      <c r="A124" s="51"/>
+      <c r="B124" s="60" t="s">
         <v>184</v>
       </c>
       <c r="C124" s="1" t="s">
@@ -4954,8 +4969,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="46"/>
-      <c r="B125" s="54"/>
+      <c r="A125" s="51"/>
+      <c r="B125" s="57"/>
       <c r="C125" s="1" t="s">
         <v>182</v>
       </c>
@@ -4967,8 +4982,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="46"/>
-      <c r="B126" s="54"/>
+      <c r="A126" s="51"/>
+      <c r="B126" s="57"/>
       <c r="C126" s="1" t="s">
         <v>178</v>
       </c>
@@ -4980,8 +4995,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="46"/>
-      <c r="B127" s="54"/>
+      <c r="A127" s="51"/>
+      <c r="B127" s="57"/>
       <c r="C127" s="1" t="s">
         <v>180</v>
       </c>
@@ -4993,8 +5008,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="46"/>
-      <c r="B128" s="54"/>
+      <c r="A128" s="51"/>
+      <c r="B128" s="57"/>
       <c r="C128" s="1" t="s">
         <v>183</v>
       </c>
@@ -5006,8 +5021,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="46"/>
-      <c r="B129" s="54"/>
+      <c r="A129" s="51"/>
+      <c r="B129" s="57"/>
       <c r="C129" s="1" t="s">
         <v>193</v>
       </c>
@@ -5019,12 +5034,12 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="46"/>
-      <c r="B130" s="54"/>
+      <c r="A130" s="51"/>
+      <c r="B130" s="57"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="46"/>
-      <c r="B131" s="57" t="s">
+      <c r="A131" s="51"/>
+      <c r="B131" s="60" t="s">
         <v>208</v>
       </c>
       <c r="C131" s="11" t="s">
@@ -5039,8 +5054,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="46"/>
-      <c r="B132" s="54"/>
+      <c r="A132" s="51"/>
+      <c r="B132" s="57"/>
       <c r="C132" s="1" t="s">
         <v>206</v>
       </c>
@@ -5052,8 +5067,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="46"/>
-      <c r="B133" s="54"/>
+      <c r="A133" s="51"/>
+      <c r="B133" s="57"/>
       <c r="C133" s="1" t="s">
         <v>217</v>
       </c>
@@ -5065,8 +5080,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="46"/>
-      <c r="B134" s="54"/>
+      <c r="A134" s="51"/>
+      <c r="B134" s="57"/>
       <c r="C134" s="1" t="s">
         <v>207</v>
       </c>
@@ -5078,8 +5093,8 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="46"/>
-      <c r="B135" s="54"/>
+      <c r="A135" s="51"/>
+      <c r="B135" s="57"/>
       <c r="C135" s="1" t="s">
         <v>312</v>
       </c>
@@ -5091,8 +5106,8 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="46"/>
-      <c r="B136" s="54"/>
+      <c r="A136" s="51"/>
+      <c r="B136" s="57"/>
       <c r="C136" s="1" t="s">
         <v>336</v>
       </c>
@@ -5104,8 +5119,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="46"/>
-      <c r="B137" s="54"/>
+      <c r="A137" s="51"/>
+      <c r="B137" s="57"/>
       <c r="C137" s="1" t="s">
         <v>338</v>
       </c>
@@ -5117,8 +5132,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="46"/>
-      <c r="B138" s="54"/>
+      <c r="A138" s="51"/>
+      <c r="B138" s="57"/>
       <c r="C138" s="1" t="s">
         <v>219</v>
       </c>
@@ -5130,8 +5145,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="46"/>
-      <c r="B139" s="54"/>
+      <c r="A139" s="51"/>
+      <c r="B139" s="57"/>
       <c r="C139" s="1" t="s">
         <v>223</v>
       </c>
@@ -5143,8 +5158,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="46"/>
-      <c r="B140" s="54"/>
+      <c r="A140" s="51"/>
+      <c r="B140" s="57"/>
       <c r="C140" s="1" t="s">
         <v>204</v>
       </c>
@@ -5156,8 +5171,8 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="46"/>
-      <c r="B141" s="54"/>
+      <c r="A141" s="51"/>
+      <c r="B141" s="57"/>
       <c r="C141" s="1" t="s">
         <v>266</v>
       </c>
@@ -5169,8 +5184,8 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="46"/>
-      <c r="B142" s="54"/>
+      <c r="A142" s="51"/>
+      <c r="B142" s="57"/>
       <c r="C142" s="1" t="s">
         <v>268</v>
       </c>
@@ -5182,12 +5197,12 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="46"/>
-      <c r="B143" s="54"/>
+      <c r="A143" s="51"/>
+      <c r="B143" s="57"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="46"/>
-      <c r="B144" s="57" t="s">
+      <c r="A144" s="51"/>
+      <c r="B144" s="60" t="s">
         <v>224</v>
       </c>
       <c r="C144" s="11" t="s">
@@ -5202,8 +5217,8 @@
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="46"/>
-      <c r="B145" s="54"/>
+      <c r="A145" s="51"/>
+      <c r="B145" s="63"/>
       <c r="C145" s="1" t="s">
         <v>314</v>
       </c>
@@ -5215,8 +5230,8 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="46"/>
-      <c r="B146" s="54"/>
+      <c r="A146" s="51"/>
+      <c r="B146" s="63"/>
       <c r="C146" s="1" t="s">
         <v>227</v>
       </c>
@@ -5228,8 +5243,8 @@
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="46"/>
-      <c r="B147" s="54"/>
+      <c r="A147" s="51"/>
+      <c r="B147" s="63"/>
       <c r="C147" s="1" t="s">
         <v>269</v>
       </c>
@@ -5241,8 +5256,8 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="46"/>
-      <c r="B148" s="54"/>
+      <c r="A148" s="51"/>
+      <c r="B148" s="63"/>
       <c r="C148" s="1" t="s">
         <v>271</v>
       </c>
@@ -5253,8 +5268,52 @@
         <v>215</v>
       </c>
     </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="51"/>
+      <c r="B149" s="61"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="51"/>
+      <c r="B150" s="60" t="s">
+        <v>390</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="E150" s="11"/>
+      <c r="F150" s="11" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="51"/>
+      <c r="B151" s="57"/>
+      <c r="C151" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="B144:B149"/>
+    <mergeCell ref="A121:A151"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="B124:B130"/>
+    <mergeCell ref="B131:B143"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="A107:A120"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="B111:B114"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
@@ -5265,19 +5324,9 @@
     <mergeCell ref="B23:B32"/>
     <mergeCell ref="B46:B55"/>
     <mergeCell ref="B56:B65"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="B124:B130"/>
-    <mergeCell ref="B144:B148"/>
-    <mergeCell ref="A121:A148"/>
-    <mergeCell ref="B131:B143"/>
-    <mergeCell ref="B121:B123"/>
     <mergeCell ref="A78:A106"/>
     <mergeCell ref="B87:B96"/>
     <mergeCell ref="B97:B106"/>
-    <mergeCell ref="A107:A120"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="B111:B114"/>
     <mergeCell ref="B78:B80"/>
     <mergeCell ref="B81:B83"/>
   </mergeCells>

--- a/Methanol/Methanol_Brownfield_Memmingen_Bio_H2/Datenbank.xlsx
+++ b/Methanol/Methanol_Brownfield_Memmingen_Bio_H2/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Brownfield_Memmingen_Bio_H2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A5E895-BB5A-4DEC-BE9C-3218ACCCB890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602E183A-FBBE-43EF-A34C-06FF80EFEE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="396">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1367,6 +1367,9 @@
   </si>
   <si>
     <t>calc_price</t>
+  </si>
+  <si>
+    <t>kWh_th/a</t>
   </si>
 </sst>
 </file>
@@ -3232,7 +3235,7 @@
         <v>-1E-4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -4102,7 +4105,7 @@
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="1" t="s">
-        <v>133</v>
+        <v>395</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -4116,7 +4119,7 @@
       </c>
       <c r="E59" s="9"/>
       <c r="F59" s="1" t="s">
-        <v>133</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -5303,17 +5306,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="B144:B149"/>
-    <mergeCell ref="A121:A151"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="B124:B130"/>
-    <mergeCell ref="B131:B143"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="A107:A120"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="B111:B114"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
@@ -5329,6 +5321,17 @@
     <mergeCell ref="B97:B106"/>
     <mergeCell ref="B78:B80"/>
     <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="B144:B149"/>
+    <mergeCell ref="A121:A151"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="B124:B130"/>
+    <mergeCell ref="B131:B143"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="A107:A120"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="B111:B114"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
